--- a/java/POS_Basket_Validation_UseCases.xlsx
+++ b/java/POS_Basket_Validation_UseCases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rameshkadem/Documents/projects/tcb/basket-validation-function/java/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C121AA6-4655-0142-A68C-B7B96E4D8450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03F4A844-179C-004C-92DA-8015D5EA443E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Offers" sheetId="1" r:id="rId1"/>
@@ -34190,197 +34190,6 @@
     {
       "product_code": "037000930396",
       "price": 1.29,
-      "quantity": 12,
-      "unit": "item"
-    },
-    {
-      "product_code": "7106919588011",
-      "price": 1.81,
-      "quantity": 13,
-      "unit": "item"
-    },
-    {
-      "product_code": "030772036433",
-      "price": 5.44,
-      "quantity": 2,
-      "unit": "item"
-    },
-    {
-      "product_code": "037000925033",
-      "price": 1.59,
-      "quantity": 13,
-      "unit": "item"
-    },
-    {
-      "product_code": "8952803493171",
-      "price": 4.67,
-      "quantity": 9,
-      "unit": "item"
-    },
-    {
-      "product_code": "037000590804",
-      "price": 5.11,
-      "quantity": 4,
-      "unit": "item"
-    },
-    {
-      "product_code": "030772094969",
-      "price": 4.76,
-      "quantity": 4,
-      "unit": "item"
-    },
-    {
-      "product_code": "2066196461818",
-      "price": 3.43,
-      "quantity": 4,
-      "unit": "item"
-    },
-    {
-      "product_code": "037000758365",
-      "price": 1.99,
-      "quantity": 13,
-      "unit": "item"
-    },
-    {
-      "product_code": "030772075258",
-      "price": 5.64,
-      "quantity": 3,
-      "unit": "item"
-    },
-    {
-      "product_code": "037000930419",
-      "price": 8.07,
-      "quantity": 11,
-      "unit": "item"
-    },
-    {
-      "product_code": "6013644404626",
-      "price": 5.35,
-      "quantity": 2,
-      "unit": "item"
-    },
-    {
-      "product_code": "030772094990",
-      "price": 2.22,
-      "quantity": 2,
-      "unit": "item"
-    },
-    {
-      "product_code": "030772076880",
-      "price": 5.52,
-      "quantity": 7,
-      "unit": "item"
-    },
-    {
-      "product_code": "5901234123457",
-      "price": 15.01,
-      "quantity": 1,
-      "unit": "item"
-    },
-    {
-      "product_code": "037000530916",
-      "price": 4.41,
-      "quantity": 3,
-      "unit": "item"
-    },
-    {
-      "product_code": "037000653172",
-      "price": 8.03,
-      "quantity": 1,
-      "unit": "item"
-    },
-    {
-      "product_code": "037000916192",
-      "price": 9.69,
-      "quantity": 1,
-      "unit": "item"
-    }
-  ],
-  "coupons": [
-    {
-      "gs1": "8112009988459000129133768829435951"
-    },
-    {
-      "gs1": "8112009988459000229133701244303370"
-    },
-    {
-      "gs1": "8112009988459000259133185516163441"
-    },
-    {
-      "gs1": "8112009988459000149133805040402560"
-    },
-    {
-      "gs1": "8112009988459000239133444997582221"
-    },
-    {
-      "gs1": "8112009988459000219133223879896350"
-    },
-    {
-      "gs1": "8112009988459000169133736410030271"
-    },
-    {
-      "gs1": "8112009988459000209133587882077150"
-    },
-    {
-      "gs1": "8112009988459000079133769222789901"
-    },
-    {
-      "gs1": "8112009988459000159133589790020941"
-    },
-    {
-      "gs1": "8112009988459000049133103414813991"
-    },
-    {
-      "gs1": "8112009988459000089133226130651620"
-    },
-    {
-      "gs1": "8112009988459000099133820075347111"
-    },
-    {
-      "gs1": "8112009988459000069133619787447350"
-    },
-    {
-      "gs1": "8112009988459000249133903816879100"
-    },
-    {
-      "gs1": "8112009988459000139133267545843870"
-    },
-    {
-      "gs1": "8112009988459000199133186009295270"
-    },
-    {
-      "gs1": "8112009988459000059133140178143621"
-    },
-    {
-      "gs1": "8112009988459000179133911731890720"
-    },
-    {
-      "gs1": "8112009988459000269133590254270211"
-    },
-    {
-      "gs1": "8112009988459000109133290291921431"
-    },
-    {
-      "gs1": "8112009988459000119133912481407941"
-    },
-    {
-      "gs1": "8112009988459000039133624659452241"
-    },
-    {
-      "gs1": "8112009988459000289133263265480791"
-    },
-    {
-      "gs1": "8112009988459000019133773047131520"
-    }
-  ]
-}</t>
-  </si>
-  <si>
-    <t>{
-  "basket": [
-    {
-      "product_code": "037000930396",
-      "price": 1.29,
       "quantity": 32,
       "unit": "item"
     },
@@ -35360,6 +35169,203 @@
           "8952803493171"
         ]
       }
+    }
+  ]
+}</t>
+  </si>
+  <si>
+    <t>{
+  "basket": [
+    {
+      "product_code": "037000930396",
+      "price": 1.29,
+      "quantity": 12,
+      "unit": "item"
+    },
+    {
+      "product_code": "7106919588011",
+      "price": 1.81,
+      "quantity": 13,
+      "unit": "item"
+    },
+    {
+      "product_code": "030772036433",
+      "price": 5.44,
+      "quantity": 2,
+      "unit": "item"
+    },
+    {
+      "product_code": "037000925033",
+      "price": 1.59,
+      "quantity": 13,
+      "unit": "item"
+    },
+    {
+      "product_code": "8952803493171",
+      "price": 4.67,
+      "quantity": 9,
+      "unit": "item"
+    },
+    {
+      "product_code": "037000590804",
+      "price": 5.11,
+      "quantity": 4,
+      "unit": "item"
+    },
+    {
+      "product_code": "030772094969",
+      "price": 4.76,
+      "quantity": 4,
+      "unit": "item"
+    },
+    {
+      "product_code": "2066196461818",
+      "price": 3.43,
+      "quantity": 4,
+      "unit": "item"
+    },
+    {
+      "product_code": "037000758365",
+      "price": 1.99,
+      "quantity": 13,
+      "unit": "item"
+    },
+    {
+      "product_code": "030772075258",
+      "price": 5.64,
+      "quantity": 3,
+      "unit": "item"
+    },
+    {
+      "product_code": "037000930419",
+      "price": 8.07,
+      "quantity": 11,
+      "unit": "item"
+    },
+    {
+      "product_code": "6013644404626",
+      "price": 5.35,
+      "quantity": 2,
+      "unit": "item"
+    },
+    {
+      "product_code": "030772094990",
+      "price": 2.22,
+      "quantity": 2,
+      "unit": "item"
+    },
+    {
+      "product_code": "030772076880",
+      "price": 5.52,
+      "quantity": 7,
+      "unit": "item"
+    },
+    {
+      "product_code": "5901234123457",
+      "price": 15.01,
+      "quantity": 1,
+      "unit": "item"
+    },
+    {
+      "product_code": "037000530916",
+      "price": 4.41,
+      "quantity": 3,
+      "unit": "item"
+    },
+    {
+      "product_code": "037000653172",
+      "price": 8.03,
+      "quantity": 1,
+      "unit": "item"
+    },
+    {
+      "product_code": "037000916192",
+      "price": 9.69,
+      "quantity": 1,
+      "unit": "item"
+    }
+  ],
+  "coupons": [
+    {
+      "gs1": "8112009988459000129133768829435951"
+    },
+    {
+      "gs1": "8112009988459000229133701244303370"
+    },
+    {
+      "gs1": "8112009988459000259133185516163441"
+    },
+    {
+      "gs1": "8112009988459000149133805040402560"
+    },
+    {
+      "gs1": "8112009988459000239133444997582221"
+    },
+    {
+      "gs1": "8112009988459000219133223879896350"
+    },
+    {
+      "gs1": "8112009988459000169133736410030271"
+    },
+    {
+      "gs1": "8112009988459000209133587882077150"
+    },
+    {
+      "gs1": "8112009988459000079133769222789901"
+    },
+    {
+      "gs1": "8112009988459000159133589790020941"
+    },
+    {
+      "gs1": "8112009988459000049133103414813991"
+    },
+    {
+      "gs1": "8112009988459000089133226130651620"
+    },
+    {
+      "gs1": "8112009988459000099133820075347111"
+    },
+    {
+      "gs1": "8112009988459000189133476128679584"
+    },
+    {
+      "gs1": "8112009988459000069133619787447350"
+    },
+    {
+      "gs1": "8112009988459000249133903816879100"
+    },
+    {
+      "gs1": "8112009988459000139133267545843870"
+    },
+    {
+      "gs1": "8112009988459000199133186009295270"
+    },
+    {
+      "gs1": "8112009988459000059133140178143621"
+    },
+    {
+      "gs1": "8112009988459000179133911731890720"
+    },
+    {
+      "gs1": "8112009988459000269133590254270211"
+    },
+    {
+      "gs1": "8112009988459000109133290291921431"
+    },
+    {
+      "gs1": "8112009988459000279133269267434310"
+    },
+    {
+      "gs1": "8112009988459000119133912481407941"
+    },
+    {
+      "gs1": "8112009988459000039133624659452241"
+    },
+    {
+      "gs1": "8112009988459000289133263265480791"
+    },
+    {
+      "gs1": "8112009988459000019133773047131520"
     }
   ]
 }</t>
@@ -42748,16 +42754,16 @@
         <v>8.1120099884590004E+33</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="G34" s="11" t="s">
         <v>420</v>
       </c>
       <c r="H34" s="44" t="s">
+        <v>1620</v>
+      </c>
+      <c r="I34" s="48" t="s">
         <v>1621</v>
-      </c>
-      <c r="I34" s="48" t="s">
-        <v>1622</v>
       </c>
       <c r="J34" s="48" t="s">
         <v>1296</v>
@@ -47023,7 +47029,7 @@
       <c r="C179" s="16"/>
       <c r="D179" s="16"/>
       <c r="E179" s="16" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="F179" s="42" t="s">
         <v>1447</v>
@@ -47107,14 +47113,14 @@
       <c r="C183" s="16"/>
       <c r="D183" s="16"/>
       <c r="E183" s="16" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="F183" s="42" t="s">
         <v>1294</v>
       </c>
       <c r="G183" s="42"/>
       <c r="H183" s="14" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="184" spans="1:8" ht="409.6" x14ac:dyDescent="0.15">
@@ -53264,7 +53270,7 @@
         <v>219</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="G5" s="11" t="s">
         <v>227</v>
@@ -54221,19 +54227,19 @@
         <v>71</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="G34" s="11" t="s">
         <v>420</v>
       </c>
       <c r="H34" s="44" t="s">
+        <v>1620</v>
+      </c>
+      <c r="I34" s="48" t="s">
         <v>1621</v>
-      </c>
-      <c r="I34" s="48" t="s">
-        <v>1622</v>
       </c>
       <c r="J34" s="48" t="s">
         <v>1296</v>
@@ -58200,7 +58206,7 @@
         <v>1213</v>
       </c>
       <c r="F165" s="17" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="G165" s="17"/>
       <c r="H165" s="57" t="s">
@@ -58499,10 +58505,10 @@
       <c r="C179" s="16"/>
       <c r="D179" s="16"/>
       <c r="E179" s="16" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="F179" s="42" t="s">
-        <v>1612</v>
+        <v>1627</v>
       </c>
       <c r="G179" s="42"/>
       <c r="H179" s="14" t="s">
@@ -58524,7 +58530,7 @@
         <v>1282</v>
       </c>
       <c r="F180" s="42" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="G180" s="42"/>
       <c r="H180" s="14" t="s">
@@ -58583,14 +58589,14 @@
       <c r="C183" s="16"/>
       <c r="D183" s="16"/>
       <c r="E183" s="16" t="s">
+        <v>1624</v>
+      </c>
+      <c r="F183" s="42" t="s">
         <v>1625</v>
-      </c>
-      <c r="F183" s="42" t="s">
-        <v>1626</v>
       </c>
       <c r="G183" s="42"/>
       <c r="H183" s="14" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="184" spans="1:8" ht="409.6" x14ac:dyDescent="0.15">
@@ -58608,7 +58614,7 @@
         <v>1474</v>
       </c>
       <c r="F184" s="42" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="H184" s="14" t="s">
         <v>1476</v>
@@ -58629,7 +58635,7 @@
         <v>1479</v>
       </c>
       <c r="F185" s="42" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="H185" s="14" t="s">
         <v>1481</v>
@@ -58650,7 +58656,7 @@
         <v>1484</v>
       </c>
       <c r="F186" s="42" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="H186" s="14" t="s">
         <v>1486</v>
@@ -58671,7 +58677,7 @@
         <v>1488</v>
       </c>
       <c r="F187" s="42" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="H187" s="14" t="s">
         <v>1490</v>
